--- a/1.0.0-ballot-rc.2/StructureDefinition-TherapiezielDreieck.xlsx
+++ b/1.0.0-ballot-rc.2/StructureDefinition-TherapiezielDreieck.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:18:27+00:00</t>
+    <t>2026-07-31T14:32:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
